--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.502467917678935</v>
+        <v>0.406651036622827</v>
       </c>
       <c r="D2" t="n">
-        <v>7.793337610492109</v>
+        <v>1.266417361704968</v>
       </c>
       <c r="E2" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F2" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.0454622926582</v>
+        <v>1.632387622556958</v>
       </c>
       <c r="D3" t="n">
-        <v>7.827929208573901</v>
+        <v>1.272038496393259</v>
       </c>
       <c r="E3" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F3" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.97586096583047</v>
+        <v>2.758577406947452</v>
       </c>
       <c r="D4" t="n">
-        <v>16.27517930438339</v>
+        <v>2.6447166369623</v>
       </c>
       <c r="E4" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F4" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.61372295176403</v>
+        <v>2.049729979661655</v>
       </c>
       <c r="D5" t="n">
-        <v>25.57551381608771</v>
+        <v>4.156020995114252</v>
       </c>
       <c r="E5" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F5" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.89502086633181</v>
+        <v>6.15794089077892</v>
       </c>
       <c r="D6" t="n">
-        <v>19.12302277360981</v>
+        <v>3.107491200711594</v>
       </c>
       <c r="E6" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F6" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.5786891081552</v>
+        <v>6.10653698007522</v>
       </c>
       <c r="D7" t="n">
-        <v>18.34015024777909</v>
+        <v>2.980274415264103</v>
       </c>
       <c r="E7" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F7" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.418540044529454</v>
+        <v>1.205512757236036</v>
       </c>
       <c r="D8" t="n">
-        <v>27.89880708509188</v>
+        <v>4.533556151327431</v>
       </c>
       <c r="E8" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F8" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2604857205668</v>
+        <v>6.217328929592105</v>
       </c>
       <c r="D9" t="n">
-        <v>23.64820615439969</v>
+        <v>3.84283350008995</v>
       </c>
       <c r="E9" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F9" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.81004524927742</v>
+        <v>7.281632353007581</v>
       </c>
       <c r="D10" t="n">
-        <v>15.9945978534575</v>
+        <v>2.599122151186844</v>
       </c>
       <c r="E10" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F10" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>72.62927391206031</v>
+        <v>11.8022570107098</v>
       </c>
       <c r="D11" t="n">
-        <v>33.68878150188466</v>
+        <v>5.474426994056258</v>
       </c>
       <c r="E11" t="n">
-        <v>20.79324889867677</v>
+        <v>3.378902946034975</v>
       </c>
       <c r="F11" t="n">
-        <v>7.894953928138907</v>
+        <v>1.282930013322573</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
